--- a/Documents/devfiles/excel/DBdesignVer2.xlsx
+++ b/Documents/devfiles/excel/DBdesignVer2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AF28B3-5EB0-421D-851D-F3ACCC99BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67D12A-50E0-458E-BF0E-71999C36CCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="23040" windowHeight="12120" activeTab="6" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="3144" yWindow="4044" windowWidth="23040" windowHeight="12120" activeTab="6" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTable" sheetId="12" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Letter" sheetId="15" r:id="rId4"/>
     <sheet name="Status" sheetId="16" r:id="rId5"/>
     <sheet name="StatusName" sheetId="17" r:id="rId6"/>
-    <sheet name="Draft" sheetId="19" r:id="rId7"/>
+    <sheet name="Draft" sheetId="20" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
   <si>
     <t>Name</t>
   </si>
@@ -372,13 +372,396 @@
   </si>
   <si>
     <t>EmailTemplateId</t>
+  </si>
+  <si>
+    <t>[ResponseId]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[DboxId]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[CSGId]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[CompanyId]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[DivisionId]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[DepartmentId]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[DboxRefNum]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[CandidateName]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Company]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Division]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Department]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[CostCenter]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[JobLevel]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[JobPosition]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[EmailAddress]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[ContactNumber]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[StatusId]</t>
+    </r>
+  </si>
+  <si>
+    <t>[DboxCandidates]</t>
+  </si>
+  <si>
+    <t>[CandidateId]</t>
+  </si>
+  <si>
+    <t>[DboxCandidatesRawData]</t>
+  </si>
+  <si>
+    <t>[Id]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,6 +787,12 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="Cascadia Mono"/>
       <family val="3"/>
     </font>
@@ -1610,10 +1999,155 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B7B37E1-E9C8-4011-B172-9D118CCEF591}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A638FA62-A166-4C10-BC01-6831EDC0EDF4}">
+  <dimension ref="B1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="E1" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G9" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Documents/devfiles/excel/DBdesignVer2.xlsx
+++ b/Documents/devfiles/excel/DBdesignVer2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67D12A-50E0-458E-BF0E-71999C36CCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03846160-79C2-4A8C-8203-018C52143271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3144" yWindow="4044" windowWidth="23040" windowHeight="12120" activeTab="6" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="3144" yWindow="4044" windowWidth="23040" windowHeight="12120" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTable" sheetId="12" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="137">
   <si>
     <t>Name</t>
   </si>
@@ -755,6 +755,27 @@
   </si>
   <si>
     <t>[Id]</t>
+  </si>
+  <si>
+    <t>JobOfferHasEmail</t>
+  </si>
+  <si>
+    <t>ToRecipient</t>
+  </si>
+  <si>
+    <t>CCRecipient</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>JOHasEmailStatus</t>
+  </si>
+  <si>
+    <t>CandidateId</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2552A1-D2D6-4D6E-936E-AAD262657723}">
-  <dimension ref="B2:H26"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
@@ -1634,9 +1655,10 @@
     <col min="6" max="6" width="19.44140625" customWidth="1"/>
     <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
@@ -1649,8 +1671,14 @@
       <c r="H2" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -1663,8 +1691,14 @@
       <c r="H3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>44</v>
       </c>
@@ -1677,8 +1711,11 @@
       <c r="H4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1688,61 +1725,76 @@
       <c r="F5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="F7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>56</v>
       </c>
@@ -1794,6 +1846,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Documents/devfiles/excel/DBdesignVer2.xlsx
+++ b/Documents/devfiles/excel/DBdesignVer2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03846160-79C2-4A8C-8203-018C52143271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53494E90-D750-41DF-B9AC-796914EB8394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3144" yWindow="4044" windowWidth="23040" windowHeight="12120" activeTab="3" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTable" sheetId="12" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Letter" sheetId="15" r:id="rId4"/>
     <sheet name="Status" sheetId="16" r:id="rId5"/>
     <sheet name="StatusName" sheetId="17" r:id="rId6"/>
-    <sheet name="Draft" sheetId="20" r:id="rId7"/>
+    <sheet name="Candidates" sheetId="20" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="143">
   <si>
     <t>Name</t>
   </si>
@@ -776,6 +776,24 @@
   </si>
   <si>
     <t>CandidateId</t>
+  </si>
+  <si>
+    <t>FileTypes</t>
+  </si>
+  <si>
+    <t>CandidateFiles</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>RelativePath</t>
+  </si>
+  <si>
+    <t>CreatedBy</t>
+  </si>
+  <si>
+    <t>DocumentType</t>
   </si>
 </sst>
 </file>
@@ -1188,16 +1206,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3E0DE8-4720-4CDB-8DB3-CDF187788EC3}">
   <dimension ref="B2:J21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1214,7 +1232,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -1231,7 +1249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -1248,12 +1266,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1264,7 +1282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -1278,7 +1296,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>26</v>
       </c>
@@ -1289,7 +1307,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -1303,7 +1321,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>5</v>
       </c>
@@ -1314,7 +1332,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>19</v>
       </c>
@@ -1325,7 +1343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F12" t="s">
         <v>10</v>
       </c>
@@ -1333,37 +1351,37 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1376,13 +1394,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5710F30C-E88B-4A3C-8A63-0D8128BE2FFF}">
   <dimension ref="B2:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
@@ -1390,7 +1408,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>38</v>
       </c>
@@ -1398,7 +1416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -1406,32 +1424,32 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
@@ -1444,15 +1462,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7AE70E-E5CC-4406-BB70-6FBBBFBDDCCE}">
   <dimension ref="B2:H26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
@@ -1466,7 +1484,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1480,7 +1498,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1491,7 +1509,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>45</v>
       </c>
@@ -1499,12 +1517,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
@@ -1512,7 +1530,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -1520,7 +1538,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>24</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>33</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>34</v>
       </c>
@@ -1552,7 +1570,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -1560,12 +1578,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
@@ -1573,7 +1591,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>11</v>
       </c>
@@ -1581,12 +1599,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>13</v>
       </c>
@@ -1594,12 +1612,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
@@ -1607,7 +1625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>7</v>
       </c>
@@ -1615,27 +1633,27 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
         <v>82</v>
       </c>
@@ -1648,17 +1666,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2552A1-D2D6-4D6E-936E-AAD262657723}">
   <dimension ref="B2:L26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
@@ -1678,7 +1696,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -1698,7 +1716,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>44</v>
       </c>
@@ -1715,7 +1733,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1729,7 +1747,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>11</v>
       </c>
@@ -1740,7 +1758,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
       <c r="F7" t="s">
         <v>6</v>
       </c>
@@ -1748,7 +1766,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
@@ -1756,7 +1774,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>47</v>
       </c>
@@ -1764,82 +1782,82 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>45</v>
       </c>
@@ -1853,16 +1871,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BADF9B9-38B5-461D-B650-FB9B2CB7966D}">
   <dimension ref="B2:J10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>67</v>
       </c>
@@ -1879,7 +1897,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>68</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>73</v>
       </c>
@@ -1910,7 +1928,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
@@ -1927,7 +1945,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>63</v>
       </c>
@@ -1941,7 +1959,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F7" t="s">
         <v>98</v>
       </c>
@@ -1949,12 +1967,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>69</v>
       </c>
@@ -1967,14 +1985,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ABED4AD-1AED-4632-9454-063816F78CB2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.33203125" customWidth="1"/>
-    <col min="3" max="3" width="72.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.36328125" customWidth="1"/>
+    <col min="3" max="3" width="72.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>83</v>
       </c>
@@ -1985,7 +2003,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>86</v>
@@ -1994,7 +2012,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>88</v>
@@ -2003,7 +2021,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>97</v>
@@ -2012,7 +2030,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>90</v>
@@ -2021,7 +2039,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>92</v>
@@ -2030,7 +2048,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>94</v>
@@ -2039,7 +2057,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>96</v>
@@ -2054,150 +2072,165 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A638FA62-A166-4C10-BC01-6831EDC0EDF4}">
   <dimension ref="B1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.36328125" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="23.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="E4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G9" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="G10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C11" s="2"/>
-      <c r="G11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12" s="2"/>
-      <c r="G12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="2" t="s">
-        <v>125</v>
-      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C18" s="2"/>
     </row>
   </sheetData>
